--- a/漢字（かんじ）/d.xlsx
+++ b/漢字（かんじ）/d.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>仮名</t>
   </si>
@@ -179,6 +179,9 @@
 団体｜だんたい</t>
   </si>
   <si>
+    <t>爆弾｜ばくだん</t>
+  </si>
+  <si>
     <t>だつ</t>
   </si>
   <si>
@@ -257,6 +260,14 @@
     <t>独立｜どくりつ
 孤独｜こどく
 独特｜どくとく</t>
+  </si>
+  <si>
+    <t>読</t>
+  </si>
+  <si>
+    <t>朗読｜ろうどく
+読書｜どくしょ
+読書感想｜どくしょかんそう</t>
   </si>
   <si>
     <t>どう</t>
@@ -331,7 +342,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,13 +368,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -813,148 +817,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1292,7 +1296,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="31.4444444444444" customWidth="1"/>
@@ -1441,15 +1445,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="36" spans="1:3">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" ht="36" spans="1:3">
+      <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>32</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1480,32 +1495,32 @@
     </row>
     <row r="2" ht="144" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="180" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
@@ -1520,7 +1535,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="25.2222222222222" customWidth="1"/>
@@ -1539,134 +1554,145 @@
     </row>
     <row r="2" ht="90" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" ht="90" spans="1:3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="72" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" ht="34.8" customHeight="1" spans="1:3">
+    <row r="7" ht="90" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="34.8" customHeight="1" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" ht="27.6" spans="1:3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" ht="54" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:3">
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" ht="27.6" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" ht="18" spans="1:3">
+      <c r="C10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="12" ht="41.4" spans="1:3">
+      <c r="C11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="13" ht="41.4" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>65</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/d.xlsx
+++ b/漢字（かんじ）/d.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="だ" sheetId="1" r:id="rId1"/>
@@ -236,7 +236,9 @@
 湿度｜しつど
 態度｜たいど
 制度｜せいど
-一度｜いちど</t>
+一度｜いちど
+高度｜こうど
+緯度｜いど</t>
   </si>
   <si>
     <t>努</t>
@@ -1552,7 +1554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="90" spans="1:3">
+    <row r="2" ht="126" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
